--- a/site/exports/tju-life-sciences.xlsx
+++ b/site/exports/tju-life-sciences.xlsx
@@ -746,7 +746,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
